--- a/Cases.xlsx
+++ b/Cases.xlsx
@@ -154,8 +154,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CasesData" displayName="CasesData" ref="A1:R65" headerRowCount="1">
-  <autoFilter ref="A1:R65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CasesData" displayName="CasesData" ref="A1:R89" headerRowCount="1">
+  <autoFilter ref="A1:R89"/>
   <tableColumns count="18">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Раздел"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -759,12 +759,12 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>AuthTests.validCredentialsOpenMainScreen</t>
+          <t>ru.edu.qamid.diploma.tests.AuthTests.validCredentialsOpenMainScreen</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Пройден; 22.10.2026; 4.906 с; allure-results.zip</t>
+          <t>Пройден; 26.10.2026; 3.863 с; allure-results.zip</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>AuthTests.emptyCredentialsRemainOnAuthorizationScreen</t>
+          <t>ru.edu.qamid.diploma.tests.AuthTests.emptyCredentialsRemainOnAuthorizationScreen</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>Пройден; 22.10.2026; 4.124 с; allure-results.zip</t>
+          <t>Пройден; 26.10.2026; 3.776 с; allure-results.zip</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>AuthTests.logoutReturnsToAuthorization</t>
+          <t>ru.edu.qamid.diploma.tests.AuthTests.logoutReturnsToAuthorization</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Пройден; 22.10.2026; 9.424 с; allure-results.zip</t>
+          <t>Пройден; 26.10.2026; 7.682 с; allure-results.zip</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>NewsTests.incompleteDateRangeIsRejected</t>
+          <t>ru.edu.qamid.diploma.tests.NewsTests.incompleteDateRangeIsRejected</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>Пройден; 22.10.2026; 9.305 с; allure-results.zip</t>
+          <t>Пройден; 26.10.2026; 7.450 с; allure-results.zip</t>
         </is>
       </c>
     </row>
@@ -3731,12 +3731,12 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>NewsRegressionTests.creationDateEqualsToday</t>
+          <t>ru.edu.qamid.diploma.tests.NewsRegressionTests.creationDateEqualsToday</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Не пройден — BUG-001; 22.10.2026; 13.568 с; allure-results.zip</t>
+          <t>Не пройден; 26.10.2026; 9.986 с; allure-results.zip; BUG-001 в Bugs.xlsx</t>
         </is>
       </c>
     </row>
@@ -4138,17 +4138,17 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Создание и наличие уникального заголовка в панели; полный контроль всех полей и повторное обновление исходного кейса не покрыты.</t>
+          <t>Создание и наличие уникального заголовка в панели проверяются на собственной будущей публикации через десять лет. Полный контроль всех полей исходного кейса не покрыт. Доступность текущей опубликованной записи после навигации проверяется отдельно TC-088.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>NewsTests.newNewsItemAppearsInControlPanel</t>
+          <t>ru.edu.qamid.diploma.tests.NewsTests.newNewsItemAppearsInControlPanel</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Пройден; 22.10.2026; 13.933 с; allure-results.zip</t>
+          <t>Пройден; 26.10.2026; 9.650 с; allure-results.zip</t>
         </is>
       </c>
     </row>
@@ -5318,17 +5318,17 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Удаление собственной записи в очистке; не заменяет самостоятельную проверку обеих лент после обновления.</t>
+          <t>TC-079 проверяет подтверждение удаления и отсутствие записи после повторной загрузки панели. Полный исходный сценарий с проверкой обеих лент не покрыт. Очистка остальных тестов может применять резервное удаление по зарегистрированному собственному ID.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>BaseUiTest cleanup (NewsTests / NewsRegressionTests)</t>
+          <t>ru.edu.qamid.diploma.tests.NewsDeleteTests.confirmedDeletionRemovesNewsAfterReload; ru.edu.qamid.diploma.support.BaseUiTest</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>Очистка выполнена в составе тестов 22.10.2026; полный TC-055 отдельно не запускался.</t>
+          <t>Частичная проверка пройдена в составе TC-079 26.10.2026; полный TC-055 отдельно не запускался; allure-results.zip</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>MissionTests.missionContainsEightQuotes</t>
+          <t>ru.edu.qamid.diploma.tests.MissionTests.missionContainsEightQuotes</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>Пройден; 22.10.2026; 6.495 с; allure-results.zip</t>
+          <t>Пройден; 26.10.2026; 4.932 с; allure-results.zip</t>
         </is>
       </c>
     </row>
@@ -5575,12 +5575,12 @@
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>MissionTests.firstQuoteCanBeExpandedAndCollapsed</t>
+          <t>ru.edu.qamid.diploma.tests.MissionTests.firstQuoteCanBeExpandedAndCollapsed</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>Пройден; 22.10.2026; 7.853 с; allure-results.zip</t>
+          <t>Пройден; 26.10.2026; 5.258 с; allure-results.zip</t>
         </is>
       </c>
     </row>
@@ -6109,6 +6109,2214 @@
       <c r="R65" s="2" t="inlineStr">
         <is>
           <t>Нет автотеста</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="180" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>TC-065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Авторизация</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Успешная авторизация в тёмной теме</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Включён ночной режим приложения.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Учебная учётная запись из задания; действительные значения переданы локальной конфигурацией. Значения пароля не записывать в доказательства.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1. Подтвердить, что активны ресурсы ночной темы. 2. Ввести действительные данные. 3. Нажать SIGN IN. 4. Проверить уникальную панель главного экрана.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Ночная тема действительно активна; авторизация открывает главный экран без аварии. После сценария исходный режим темы восстановлен.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.DarkModeTests.validCredentialsAuthorizeInNightMode</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 4.901 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="180" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>TC-066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Авторизация / доступность</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Читаемость введённого логина в тёмной теме</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Активен ночной режим приложения.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Нейтральные данные ContrastSample и Synthetic123, не являющиеся учётными данными. Выбранный QA-критерий: контраст обычного текста ≥ 4,5:1; WCAG 2.2 SC 1.4.3: https://www.w3.org/WAI/WCAG22/Understanding/contrast-minimum.html</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1. Подтвердить активность ночной темы. 2. Заполнить поля нейтральными значениями. 3. Скрыть клавиатуру. 4. Зафиксировать снимок экрана. 5. Измерить контраст отображаемого текста логина и фона поля.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Текст логина читается на фоне поля; выбранный критерий контраста ≥ 4,5:1 выполняется. Снимок содержит только нейтральные данные. Исходная тема восстанавливается.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест не пройден. См. BUG-002 в Bugs.xlsx.</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>docs/evidence/expanded-2026-10-26/BUG-002-dark-auth.png; Bugs.xlsx: BUG-002</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.DarkModeTests.loginFieldHasReadableContrastInNightMode</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден; 26.10.2026; 4.909 с; allure-results.zip; BUG-002 в Bugs.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="180" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>TC-067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Переход из Новостей на Главную через меню</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Учебная учётная запись из задания; действительные значения переданы локальной конфигурацией. Значения пароля не записывать в доказательства.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1. Выполнить вход. 2. Через меню открыть Новости. 3. Открыть меню и выбрать Главная. 4. Проверить уникальную панель главного экрана.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Открыт именно главный экран, а не другой раздел с такой же кнопкой меню; приложение не завершается аварийно.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NavigationTests.newsMenuReturnsToMain</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 6.005 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="180" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>TC-068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Переход из Панели управления на Главную</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Учебная учётная запись из задания; действительные значения переданы локальной конфигурацией. Значения пароля не записывать в доказательства.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть меню Панели управления. 2. Выбрать Главная. 3. Проверить уникальную панель главного экрана.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Открыт главный экран; элементы панели управления не подменяют признак главного экрана.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NavigationTests.panelMenuOpensMain</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 6.186 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="180" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>TC-069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Переход из Панели управления в Новости</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Учебная учётная запись из задания; действительные значения переданы локальной конфигурацией. Значения пароля не записывать в доказательства.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть меню Панели управления. 2. Выбрать Новости. 3. Проверить уникальную панель экрана Новостей.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Открыт раздел Новостей; переход завершается без аварии.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NavigationTests.panelMenuOpensNews</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 6.259 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="180" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>TC-070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Переход из Нашей миссии в Новости</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Учебная учётная запись из задания; действительные значения переданы локальной конфигурацией. Значения пароля не записывать в доказательства.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1. Выполнить вход. 2. Открыть Нашу миссию. 3. Через меню выбрать Новости. 4. Проверить уникальную панель раздела Новостей.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Открыт раздел Новостей; экран миссии заменён требуемым разделом без аварии.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NavigationTests.missionMenuOpensNews</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 4.838 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="180" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>TC-071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Системный Back из Нашей миссии возвращает на Главную</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Учебная учётная запись из задания; действительные значения переданы локальной конфигурацией. Значения пароля не записывать в доказательства.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1. Выполнить вход. 2. С главного экрана открыть Нашу миссию. 3. Нажать системный Back. 4. Проверить уникальную панель главного экрана.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Возврат выполняется к исходному главному экрану; приложение остаётся открытым.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NavigationTests.missionBackReturnsToMain</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 4.516 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="180" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>TC-072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Системный Back из Панели управления возвращает в Новости</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Учебная учётная запись из задания; действительные значения переданы локальной конфигурацией. Значения пароля не записывать в доказательства.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать системный Back в Панели управления. 2. Проверить уникальную панель раздела Новостей.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Открывается исходный раздел Новостей без перехода на другой экран и без аварии.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NavigationTests.panelBackReturnsToNews</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 5.322 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="180" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>TC-073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Переход ALL NEWS с главного экрана</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Учебная учётная запись из задания; действительные значения переданы локальной конфигурацией. Значения пароля не записывать в доказательства.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>1. Выполнить вход. 2. При необходимости раскрыть блок новостей. 3. Нажать ALL NEWS. 4. Проверить уникальную панель раздела Новостей.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Ссылка ALL NEWS открывает раздел Новостей.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NavigationTests.allNewsShortcutOpensNews</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 4.796 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="180" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>TC-074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Авторизация / навигация</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Выход из раздела Новостей</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Учебная учётная запись из задания; действительные значения переданы локальной конфигурацией. Значения пароля не записывать в доказательства.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1. Выполнить вход. 2. Открыть Новости. 3. Открыть меню авторизации и выбрать Log out. 4. Проверить экран Authorization.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Пользователь выходит из сессии; открыт экран Authorization с доступной кнопкой входа.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NavigationTests.newsLogoutReturnsToAuthorization</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 5.847 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="180" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>TC-075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Авторизация / навигация</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Выход из Панели управления</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Учебная учётная запись из задания; действительные значения переданы локальной конфигурацией. Значения пароля не записывать в доказательства.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1. В Панели управления открыть меню авторизации. 2. Выбрать Log out. 3. Проверить экран Authorization.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен выход из сессии; открыт экран Authorization.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NavigationTests.panelLogoutReturnsToAuthorization</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 6.251 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="180" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>TC-076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Авторизация / навигация</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Выход из Нашей миссии</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Учебная учётная запись из задания; действительные значения переданы локальной конфигурацией. Значения пароля не записывать в доказательства.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1. Выполнить вход. 2. Открыть Нашу миссию. 3. Открыть меню авторизации и выбрать Log out. 4. Проверить экран Authorization.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен выход из сессии; открыт экран Authorization.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NavigationTests.missionLogoutReturnsToAuthorization</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 5.478 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="180" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>TC-077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Создание</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждённая отмена создания заполненной новости</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость с уникальным заголовком QA_DIPLOMA_&lt;UUID&gt;, категорией «Объявление», описанием «Diploma UI test», датой публикации через десять лет и временем 00:01. После проверки удалить только созданные сценарием записи.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть форму создания. 2. Заполнить все поля собственными уникальными данными. 3. Нажать Отмена. 4. Подтвердить отмену в диалоге. 5. Повторно открыть панель и проверить отсутствие точного заголовка.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Форма закрывается без сохранения; собственная запись с этим заголовком отсутствует в панели после повторного открытия.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsTests.cancelledCreationDoesNotCreateNews</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 10.310 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="180" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>TC-078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Удаление</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Отмена удаления сохраняет собственную новость</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость с уникальным заголовком QA_DIPLOMA_&lt;UUID&gt;, категорией «Объявление», описанием «Diploma UI test», датой публикации через десять лет и временем 00:01. После проверки удалить только созданные сценарием записи.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1. Создать собственную новость. 2. У этой карточки нажать Удалить. 3. В диалоге отменить удаление. 4. Повторно открыть панель. 5. Найти точный заголовок собственной новости.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>После отмены удаления собственная новость остаётся в панели. Чужие записи не изменяются.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsDeleteTests.cancelledDeletionPreservesNews</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 11.902 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="180" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>TC-079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Удаление</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждённое удаление сохраняется после повторного открытия панели</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость с уникальным заголовком QA_DIPLOMA_&lt;UUID&gt;, категорией «Объявление», описанием «Diploma UI test», датой публикации через десять лет и временем 00:01. После проверки удалить только созданные сценарием записи.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1. Создать собственную новость. 2. Нажать Удалить у карточки с её точным заголовком. 3. Подтвердить удаление. 4. Дождаться исчезновения записи. 5. Повторно открыть панель и проверить отсутствие точного заголовка.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость удалена и не появляется после повторного открытия панели; чужие записи не удаляются.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsDeleteTests.confirmedDeletionRemovesNewsAfterReload</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 10.693 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="180" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>TC-080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Сохранение изменённого заголовка собственной новости</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость с уникальным заголовком QA_DIPLOMA_&lt;UUID&gt;, категорией «Объявление», описанием «Diploma UI test», датой публикации через десять лет и временем 00:01. После проверки удалить только созданные сценарием записи. Новый заголовок: исходный + _edited.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1. Создать собственную новость. 2. Открыть её редактирование. 3. Изменить только заголовок. 4. Сохранить. 5. Повторно открыть панель и редактирование по новому точному заголовку. 6. Сверить все поля формы.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Сохранён новый заголовок; категория, описание, дата и время публикации не изменились.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsEditTests.editedTitlePersistsAfterReload</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 12.349 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="180" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>TC-081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Сохранение категории, описания, даты и времени новости</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость с уникальным заголовком QA_DIPLOMA_&lt;UUID&gt;, категорией «Объявление», описанием «Diploma UI test», датой публикации через десять лет и временем 00:01. После проверки удалить только созданные сценарием записи. Новые значения: категория «День рождения», описание «Edited diploma description», дата через одиннадцать лет, время 23:47.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1. Создать собственную новость. 2. Открыть редактирование. 3. Изменить категорию, описание, дату и время. 4. Сохранить. 5. Повторно открыть панель и форму этой новости. 6. Сверить все поля.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Категория, описание, дата и время соответствуют сохранённым значениям; заголовок остаётся прежним.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsEditTests.editedFieldsPersistAfterReload</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 15.056 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="180" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>TC-082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждённая отмена редактирования сохраняет исходные данные</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость с уникальным заголовком QA_DIPLOMA_&lt;UUID&gt;, категорией «Объявление», описанием «Diploma UI test», датой публикации через десять лет и временем 00:01. После проверки удалить только созданные сценарием записи. Несохранённый заголовок: исходный + _discarded; описание «Unsaved description».</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1. Создать собственную новость. 2. Изменить заголовок и описание в форме редактирования. 3. Нажать Отмена и подтвердить. 4. Повторно открыть панель и редактирование исходной новости. 5. Сверить исходные поля.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Изменения отменены; сохранены исходные заголовок, описание, категория, дата и время.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsEditTests.cancelledEditPreservesOriginalFields</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 12.605 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="180" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>TC-083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Отмена диалога отмены сохраняет черновик редактирования</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость с уникальным заголовком QA_DIPLOMA_&lt;UUID&gt;, категорией «Объявление», описанием «Diploma UI test», датой публикации через десять лет и временем 00:01. После проверки удалить только созданные сценарием записи. Новый заголовок: исходный + _retained.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1. Создать собственную новость. 2. В редактировании изменить заголовок. 3. Нажать Отмена. 4. В диалоге отказаться от отмены. 5. Проверить черновик. 6. Сохранить. 7. Повторно открыть форму и сверить поля.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>После закрытия диалога черновик остаётся в форме; последующее сохранение сохраняет новый заголовок и остальные исходные поля.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsEditTests.dismissedCancellationKeepsDraft</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 12.971 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="180" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>TC-084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование / дата</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждение календаря без изменений сохраняет дату публикации</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость QA_DIPLOMA_&lt;UUID&gt;, категория «Объявление», описание «Diploma UI test», дата публикации — текущая дата плюс три дня, время 23:47, Active. После сценария удалить собственную запись.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1. Создать собственную новость с будущей датой. 2. Открыть редактирование. 3. Открыть календарь сохранённой даты. 4. Подтвердить календарь, не меняя выбор. 5. Сверить все поля формы. 6. При очистке выйти без сохранения.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>В поле остаётся сохранённая будущая дата; открытие и подтверждение календаря без изменения выбора не меняет дату новости.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест не пройден. См. BUG-003 в Bugs.xlsx.</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>docs/evidence/expanded-2026-10-26/BUG-003-date-picker.png; Bugs.xlsx: BUG-003</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsEditTests.unchangedDatePickerPreservesSavedDate</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден; 26.10.2026; 11.225 с; allure-results.zip; BUG-003 в Bugs.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="180" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>TC-085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование / время</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждение выбора времени без изменений сохраняет 23:47</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Приложение установлено на API 36, доступен учебный backend, переданы действительные учебные данные. Каждый сценарий начинает с экрана Authorization. Выполнить вход; открыть Новости → Панель управления.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость QA_DIPLOMA_&lt;UUID&gt;, категория «Объявление», описание «Diploma UI test», дата публикации — текущая дата плюс три дня, время 23:47, Active. После сценария удалить собственную запись.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1. Создать собственную новость со временем 23:47. 2. Открыть редактирование. 3. Открыть выбор сохранённого времени. 4. Подтвердить диалог, не меняя выбор. 5. Сверить все поля формы. 6. При очистке выйти без сохранения.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>В поле остаётся 23:47; подтверждение диалога без изменения выбора не подменяет сохранённое время текущим.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест не пройден. См. BUG-003 в Bugs.xlsx.</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>docs/evidence/expanded-2026-10-26/BUG-003-time-picker.png; Bugs.xlsx: BUG-003</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>Граница покрытия соответствует указанным шагам и проверяемым полям; результат подтверждается отдельным прогоном.</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsEditTests.unchangedTimePickerPreservesSavedTime</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден; 26.10.2026; 11.110 с; allure-results.zip; BUG-003 в Bugs.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="180" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>TC-086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование / активность</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Сохранение переключения активности собственной новости</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Действительная учебная учётная запись передана через локальную конфигурацию; значения не включать в доказательства. Доступна панель управления.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость QA_DIPLOMA_&lt;UUID&gt;, категория «Объявление», описание «Diploma UI test», дата публикации — текущая дата плюс десять лет, время 00:01, Active. После сценария удалить только зарегистрированную собственную запись.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>1. Создать собственную активную новость. 2. Открыть редактирование и выключить Active. 3. Сохранить, заново открыть панель и проверить статус и поля. 4. Снова включить Active, сохранить и повторно открыть панель.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>После первого сохранения статус Not Active и остальные поля прочитаны повторно и соответствуют ожиданиям. После обратного переключения и новой загрузки панели отображается статус Active.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>Самостоятельный сценарий с проверкой заявленного результата.</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsEditTests.activityChangesPersistAfterReload</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 13.841 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="180" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>TC-087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Новости / фильтрация</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Сброс пустого фильтра восстанавливает ленту без сообщения о пустом списке</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Действительная учебная учётная запись передана через локальную конфигурацию; значения не включать в доказательства. В публичной ленте есть хотя бы одна опубликованная новость; запомнить её заголовок.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Наблюдаемый заголовок существующей опубликованной новости. Период — завтрашняя дата от 00:00 до 23:59.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть Новости и запомнить заголовок опубликованной новости. 2. Применить диапазон дат на завтра. 3. Проверить пустой список. 4. Снова открыть фильтр и применить пустые поля дат. 5. Проверить возврат исходной новости и отсутствие сообщения о пустой ленте.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>В завтрашнем диапазоне нет уже опубликованных новостей. После сброса исходная новость снова доступна, сообщение о пустом списке скрыто.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>Самостоятельный сценарий с проверкой заявленного результата.</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsTests.clearingEmptyFilterHidesEmptyMessage</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>Пройден; 26.10.2026; 8.462 с; allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="180" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>TC-088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Навигация / доступность новости</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Созданная опубликованная новость доступна после перехода между разделами</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Действительная учебная учётная запись передана через локальную конфигурацию; значения не включать в доказательства. Доступна панель управления. Общая лента содержит новости с разными датами публикации.</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Собственная новость QA_DIPLOMA_&lt;UUID&gt;, категория «Объявление», описание «Diploma UI test», дата публикации — текущая дата, время 00:01, Active. Запомнить ID созданной карточки для очистки.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1. Создать собственную новость с текущей датой публикации. 2. Проверить точный заголовок в панели. 3. Через меню перейти в Новости и снова в Панель управления. 4. Дождаться завершения обновления и проверить доступность той же карточки.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Созданная новость остаётся доступна в панели после повторного чтения; навигация не лишает доступа к записи.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден (UI)</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест не пройден. См. BUG-004 в Bugs.xlsx.</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>docs/evidence/expanded-2026-10-26/BUG-004-news-after-navigation.png; Bugs.xlsx: BUG-004</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Реализована</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Полное</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>Самостоятельный сценарий с проверкой заявленного результата.</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>ru.edu.qamid.diploma.tests.NewsRegressionTests.publishedNewsRemainsAfterSectionNavigation</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден; 26.10.2026; 30.172 с; allure-results.zip; BUG-004 в Bugs.xlsx</t>
         </is>
       </c>
     </row>
